--- a/学生社团明细表.xlsx
+++ b/学生社团明细表.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12525"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="12月22日核对" sheetId="4" r:id="rId1"/>
+    <sheet name="12月24日核对" sheetId="4" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'12月24日核对'!$A$1:$G$1014</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5851" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6085" uniqueCount="1081">
   <si>
     <t>学部</t>
   </si>
@@ -3147,6 +3150,129 @@
   </si>
   <si>
     <t>朱雅文</t>
+  </si>
+  <si>
+    <t>25106班</t>
+  </si>
+  <si>
+    <t>熊辛栎</t>
+  </si>
+  <si>
+    <t>石龙宇</t>
+  </si>
+  <si>
+    <t>贺思恩</t>
+  </si>
+  <si>
+    <t>刘峻熙</t>
+  </si>
+  <si>
+    <t>刘安顺</t>
+  </si>
+  <si>
+    <t>陈志航</t>
+  </si>
+  <si>
+    <t>赵鑫锐</t>
+  </si>
+  <si>
+    <t>袁用榛</t>
+  </si>
+  <si>
+    <t>田子承</t>
+  </si>
+  <si>
+    <t>徐嘉阳</t>
+  </si>
+  <si>
+    <t>董泽涛</t>
+  </si>
+  <si>
+    <t>阮旋影</t>
+  </si>
+  <si>
+    <t>王梓炫</t>
+  </si>
+  <si>
+    <t>邱子熙</t>
+  </si>
+  <si>
+    <t>邵昌乐</t>
+  </si>
+  <si>
+    <t>叶鑫锐</t>
+  </si>
+  <si>
+    <t>胡淇然</t>
+  </si>
+  <si>
+    <t>张牵富</t>
+  </si>
+  <si>
+    <t>孙志杰</t>
+  </si>
+  <si>
+    <t>王诗翔</t>
+  </si>
+  <si>
+    <t>王子涵</t>
+  </si>
+  <si>
+    <t>谢良雨</t>
+  </si>
+  <si>
+    <t>刘涛豪</t>
+  </si>
+  <si>
+    <t>孙登峰</t>
+  </si>
+  <si>
+    <t>黄俊霖</t>
+  </si>
+  <si>
+    <t>杨成鑫</t>
+  </si>
+  <si>
+    <t>刘铭帅</t>
+  </si>
+  <si>
+    <t>郭天佑</t>
+  </si>
+  <si>
+    <t>许思博</t>
+  </si>
+  <si>
+    <t>马佳乐</t>
+  </si>
+  <si>
+    <t>毛祖龙</t>
+  </si>
+  <si>
+    <t>黄光佑</t>
+  </si>
+  <si>
+    <t>王子浩</t>
+  </si>
+  <si>
+    <t>杨广宇</t>
+  </si>
+  <si>
+    <t>张哲恺</t>
+  </si>
+  <si>
+    <t>江源</t>
+  </si>
+  <si>
+    <t>毛韵熙</t>
+  </si>
+  <si>
+    <t>袁梦雨</t>
+  </si>
+  <si>
+    <t>雷丹妮</t>
+  </si>
+  <si>
+    <t>胡子涵</t>
   </si>
 </sst>
 </file>
@@ -4584,7 +4710,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G975"/>
+  <dimension ref="A1:G1014"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -27021,7 +27147,907 @@
         <v>13094294447</v>
       </c>
     </row>
+    <row r="976" spans="1:7">
+      <c r="A976" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B976" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C976" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D976" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E976" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F976" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G976" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="977" spans="1:7">
+      <c r="A977" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B977" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C977" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D977" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E977" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F977" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G977" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="978" spans="1:7">
+      <c r="A978" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B978" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C978" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D978" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E978" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F978" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G978" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="979" spans="1:7">
+      <c r="A979" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B979" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C979" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D979" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E979" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F979" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G979" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="980" spans="1:7">
+      <c r="A980" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B980" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C980" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D980" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E980" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F980" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G980" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="981" spans="1:7">
+      <c r="A981" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B981" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C981" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D981" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E981" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F981" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G981" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="982" spans="1:7">
+      <c r="A982" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B982" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C982" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D982" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E982" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F982" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G982" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="983" spans="1:7">
+      <c r="A983" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B983" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C983" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D983" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E983" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F983" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G983" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="984" spans="1:7">
+      <c r="A984" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B984" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C984" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D984" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E984" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F984" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G984" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="985" spans="1:7">
+      <c r="A985" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B985" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C985" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D985" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E985" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F985" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G985" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="986" spans="1:7">
+      <c r="A986" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B986" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C986" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D986" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E986" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F986" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G986" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="987" spans="1:7">
+      <c r="A987" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B987" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C987" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D987" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E987" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F987" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G987" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="988" spans="1:7">
+      <c r="A988" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B988" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C988" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D988" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E988" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F988" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G988" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="989" spans="1:7">
+      <c r="A989" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B989" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C989" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D989" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E989" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F989" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G989" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="990" spans="1:7">
+      <c r="A990" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B990" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C990" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D990" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E990" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F990" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G990" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="991" spans="1:7">
+      <c r="A991" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B991" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C991" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D991" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E991" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F991" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G991" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="992" spans="1:7">
+      <c r="A992" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B992" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C992" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D992" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E992" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F992" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G992" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="993" spans="1:7">
+      <c r="A993" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B993" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C993" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D993" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E993" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F993" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G993" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="994" spans="1:7">
+      <c r="A994" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B994" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C994" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D994" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E994" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F994" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G994" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="995" spans="1:7">
+      <c r="A995" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B995" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C995" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D995" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E995" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F995" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G995" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="996" spans="1:7">
+      <c r="A996" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B996" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C996" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D996" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E996" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F996" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G996" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="997" spans="1:7">
+      <c r="A997" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B997" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C997" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D997" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E997" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F997" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G997" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="998" spans="1:7">
+      <c r="A998" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B998" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C998" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D998" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E998" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F998" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G998" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="999" spans="1:7">
+      <c r="A999" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B999" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C999" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D999" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E999" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F999" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G999" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:7">
+      <c r="A1000" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1000" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1000" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D1000" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1000" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1000" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1000" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:7">
+      <c r="A1001" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1001" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1001" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D1001" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1001" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1001" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1001" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:7">
+      <c r="A1002" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1002" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1002" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D1002" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1002" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1002" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1002" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:7">
+      <c r="A1003" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1003" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1003" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D1003" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1003" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1003" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1003" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:7">
+      <c r="A1004" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1004" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1004" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D1004" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1004" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1004" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1004" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:7">
+      <c r="A1005" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1005" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1005" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D1005" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1005" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1005" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1005" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:7">
+      <c r="A1006" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1006" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1006" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D1006" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1006" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1006" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1006" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:7">
+      <c r="A1007" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1007" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1007" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D1007" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1007" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1007" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1007" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:7">
+      <c r="A1008" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1008" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1008" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D1008" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1008" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1008" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1008" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:7">
+      <c r="A1009" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1009" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1009" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D1009" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1009" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1009" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1009" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:7">
+      <c r="A1010" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1010" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1010" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D1010" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1010" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1010" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1010" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:7">
+      <c r="A1011" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1011" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1011" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D1011" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1011" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1011" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1011" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:7">
+      <c r="A1012" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1012" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1012" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D1012" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1012" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1012" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1012" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:7">
+      <c r="A1013" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1013" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1013" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D1013" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1013" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1013" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1013" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:7">
+      <c r="A1014" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B1014" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C1014" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D1014" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1014" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1014" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G1014" s="1">
+        <v>16622971510</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G1014" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <sortState ref="A2:G975">
     <sortCondition ref="A2:A975"/>
     <sortCondition ref="B2:B975"/>
